--- a/consent_forms/032_payroll_record_review_consent_form--consent_forms.xlsx
+++ b/consent_forms/032_payroll_record_review_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Payroll Record Review</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please fill in your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
+          <t>Have you reviewed your payroll records?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,20 +575,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How often do you review your payroll records?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How many times in a month</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,13 +602,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,20 +625,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What time do you work?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HH -MM 24h format</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,13 +652,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is your email address?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>your@email.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +679,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
+          <t>Total hours worked last week?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +702,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Hours worked last week by department?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select department name for each hour worked</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,10 +729,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you want to receive updates on your time-off balance?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one or more options</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,13 +756,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
+          <t>What is your job title?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +779,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your department?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select department name</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +806,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your reporting manager?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select manager name</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,20 +833,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you consent to share your pay stub information with your manager?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select one or more options</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,13 +860,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What date was the last payday?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Date format - 2024-09-01, 2024-09-15</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,13 +887,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Review and Consent</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Do you consent to share your payroll records with the HR department?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select one or more options</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,11 +912,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -901,12 +945,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -918,46 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>payroll_record_review_consent_form_page_4_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>payroll_record_review_consent_form_page_4_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
